--- a/AAII_Financials/Yearly/ROKU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ROKU_YR_FIN.xlsx
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2400</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="3">
         <v>29600</v>
@@ -1129,7 +1129,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4737500</v>
+        <v>4733900</v>
       </c>
       <c r="E17" s="3">
         <v>4300100</v>
@@ -1180,7 +1180,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-300</v>
+        <v>3300</v>
       </c>
       <c r="E18" s="3">
         <v>-187200</v>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>376700</v>
+        <v>380300</v>
       </c>
       <c r="E21" s="3">
         <v>179100</v>
